--- a/DataRetrieved/Levels.xlsx
+++ b/DataRetrieved/Levels.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="10">
   <si>
     <t>Level</t>
   </si>

--- a/DataRetrieved/Levels.xlsx
+++ b/DataRetrieved/Levels.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="14">
   <si>
     <t>Level</t>
   </si>
@@ -42,6 +42,18 @@
   </si>
   <si>
     <t>1,645</t>
+  </si>
+  <si>
+    <t>6,917</t>
+  </si>
+  <si>
+    <t>4,577</t>
+  </si>
+  <si>
+    <t>496</t>
+  </si>
+  <si>
+    <t>1,243</t>
   </si>
 </sst>
 </file>

--- a/DataRetrieved/Levels.xlsx
+++ b/DataRetrieved/Levels.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="18">
   <si>
     <t>Level</t>
   </si>
@@ -54,6 +54,18 @@
   </si>
   <si>
     <t>1,243</t>
+  </si>
+  <si>
+    <t>5,341</t>
+  </si>
+  <si>
+    <t>4,619</t>
+  </si>
+  <si>
+    <t>503</t>
+  </si>
+  <si>
+    <t>1,595</t>
   </si>
 </sst>
 </file>
@@ -114,7 +126,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -122,7 +134,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -130,7 +142,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -138,7 +150,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/DataRetrieved/Levels.xlsx
+++ b/DataRetrieved/Levels.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="18">
   <si>
     <t>Level</t>
   </si>

--- a/DataRetrieved/Levels.xlsx
+++ b/DataRetrieved/Levels.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="18">
   <si>
     <t>Level</t>
   </si>

--- a/DataRetrieved/Levels.xlsx
+++ b/DataRetrieved/Levels.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="18">
   <si>
     <t>Level</t>
   </si>
